--- a/artfynd/A 30287-2023 artfynd.xlsx
+++ b/artfynd/A 30287-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>123421665</v>
       </c>
       <c r="B2" t="n">
-        <v>58126</v>
+        <v>58132</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>123608906</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>57378</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -920,6 +920,120 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123715945</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57857</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Backen, Liden, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>592897</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6951863</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Beatrice Berg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Beatrice Berg, Michael Englevid</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30287-2023 artfynd.xlsx
+++ b/artfynd/A 30287-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123421665</v>
       </c>
       <c r="B2" t="n">
-        <v>58132</v>
+        <v>58135</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>123608906</v>
       </c>
       <c r="B3" t="n">
-        <v>57378</v>
+        <v>57381</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>123715945</v>
       </c>
       <c r="B4" t="n">
-        <v>57857</v>
+        <v>57860</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 30287-2023 artfynd.xlsx
+++ b/artfynd/A 30287-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123421665</v>
       </c>
       <c r="B2" t="n">
-        <v>58135</v>
+        <v>58136</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>123608906</v>
       </c>
       <c r="B3" t="n">
-        <v>57381</v>
+        <v>57382</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>123715945</v>
       </c>
       <c r="B4" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Beatrice Berg, Michael Englevid</t>
+          <t>Michael Englevid, Beatrice Berg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 30287-2023 artfynd.xlsx
+++ b/artfynd/A 30287-2023 artfynd.xlsx
@@ -1030,7 +1030,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Michael Englevid, Beatrice Berg</t>
+          <t>Beatrice Berg, Michael Englevid</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 30287-2023 artfynd.xlsx
+++ b/artfynd/A 30287-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123421665</v>
+        <v>123608906</v>
       </c>
       <c r="B2" t="n">
-        <v>58158</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103042</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,14 +705,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -757,22 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,44 +782,39 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Beatrice Berg</t>
+          <t>Beatrice Englevid</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Beatrice Berg</t>
+          <t>Beatrice Englevid</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123608906</v>
+        <v>113522862</v>
       </c>
       <c r="B3" t="n">
-        <v>57404</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -841,7 +831,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -851,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592897</v>
+        <v>592849</v>
       </c>
       <c r="R3" t="n">
         <v>6951863</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,22 +871,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,44 +901,39 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Beatrice Berg</t>
+          <t>Stefan Morell</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Beatrice Berg</t>
+          <t>Stefan Morell, Leif Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123715945</v>
+        <v>113522855</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100090</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -965,7 +950,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -975,13 +960,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592897</v>
+        <v>592849</v>
       </c>
       <c r="R4" t="n">
         <v>6951863</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1005,12 +990,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,15 +1020,473 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Beatrice Berg</t>
+          <t>Stefan Morell</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Beatrice Berg, Michael Englevid</t>
+          <t>Stefan Morell, Leif Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123715945</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Backen, Liden, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>592897</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6951863</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Beatrice Englevid</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Beatrice Englevid, Michael Englevid</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>113522883</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Backen, Liden, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>592849</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6951863</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Stefan Morell</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Stefan Morell, Leif Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123421665</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Backen, Liden, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>592897</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6951863</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Beatrice Englevid</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Beatrice Englevid</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113522879</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Backen, Liden, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>592849</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6951863</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Stefan Morell</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Stefan Morell, Leif Johansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30287-2023 artfynd.xlsx
+++ b/artfynd/A 30287-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123608906</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113522862</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113522855</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1138,6 +1158,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123715945</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1253,6 +1278,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113522883</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1372,6 +1402,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123421665</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1487,8 +1522,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113522879</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>